--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.14.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="39" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,24 +605,28 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: æ—¥</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+65E5 CJK UNIFIED IDEOGRAPH-65E5 | isolated marker/symbol line :: 日</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: /</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,10 +674,14 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 26</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +693,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: a</t>
+          <t>L3: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -722,11 +734,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the Parliament of Upper Canada,â€”7th Wm. 4, ch. 2,</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -736,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: -</t>
+          <t>L5: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -758,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -773,19 +781,19 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cery in England" in respect of the following matters :â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: /</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr"/>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 26</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -825,10 +833,14 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L41: symbol-only separator/garbage line :: 837.</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr"/>
+          <t>L35: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L62: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -868,7 +880,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 4</t>
+          <t>L41: symbol-only separator/garbage line :: 837.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -911,7 +923,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 01</t>
+          <t>L42: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -954,7 +966,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L61: symbol-only separator/garbage line :: 1837.</t>
+          <t>L53: isolated marker/symbol line :: 01</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -977,12 +989,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -995,7 +1007,11 @@
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L61: symbol-only separator/garbage line :: 1837.</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1021,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1055,12 +1071,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1138,7 +1154,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
